--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondToStock001Position.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondToStock001Position.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -38,12 +38,6 @@
     <t>转债名称</t>
   </si>
   <si>
-    <t>持有券面总额</t>
-  </si>
-  <si>
-    <t>可转换券面总额</t>
-  </si>
-  <si>
     <t>纯债溢价率</t>
   </si>
   <si>
@@ -90,14 +84,23 @@
   </si>
   <si>
     <t>投资目的</t>
+  </si>
+  <si>
+    <t>持有券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可转换券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -144,7 +147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -162,6 +165,15 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,8 +462,8 @@
     <col min="2" max="2" width="26.25" customWidth="1"/>
     <col min="3" max="3" width="27.75" customWidth="1"/>
     <col min="4" max="4" width="31.5" customWidth="1"/>
-    <col min="5" max="5" width="31.375" customWidth="1"/>
-    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="31.375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="8" customWidth="1"/>
     <col min="7" max="7" width="16.25" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="16.125" customWidth="1"/>
@@ -483,67 +495,69 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
       <c r="L2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>